--- a/docs/reports/內在價值報告_20261021.xlsx
+++ b/docs/reports/內在價值報告_20261021.xlsx
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>531.877</v>
+        <v>542.33</v>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AE14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>249.5</v>
+        <v>254.975</v>
       </c>
       <c r="E25" s="8" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr">
@@ -3616,22 +3616,22 @@
       </c>
       <c r="H25" s="8" t="inlineStr"/>
       <c r="I25" s="9" t="n">
-        <v>480.8226</v>
+        <v>480.8176</v>
       </c>
       <c r="J25" s="9" t="n">
         <v>9.3416</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>17.7724</v>
+        <v>17.7712</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>-48.1</v>
+        <v>-47</v>
       </c>
       <c r="M25" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>360.6169</v>
+        <v>360.6132</v>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="AE25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AF25" s="8" t="inlineStr">
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="D48" s="24" t="n">
-        <v>346.2</v>
+        <v>343.09</v>
       </c>
       <c r="E48" s="23" t="inlineStr"/>
       <c r="F48" s="22" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="H48" s="23" t="inlineStr"/>
       <c r="I48" s="24" t="n">
-        <v>49.1601</v>
+        <v>49.1602</v>
       </c>
       <c r="J48" s="24" t="n">
         <v>9.446</v>
@@ -6405,13 +6405,13 @@
         <v>34.7808</v>
       </c>
       <c r="L48" s="25" t="n">
-        <v>604.2</v>
+        <v>597.9</v>
       </c>
       <c r="M48" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N48" s="24" t="n">
-        <v>36.8701</v>
+        <v>36.8702</v>
       </c>
       <c r="O48" s="22" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AE48" s="22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AF48" s="23" t="inlineStr">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="D52" s="24" t="n">
-        <v>344.1</v>
+        <v>332.17</v>
       </c>
       <c r="E52" s="23" t="inlineStr"/>
       <c r="F52" s="22" t="inlineStr">
@@ -6880,16 +6880,16 @@
       </c>
       <c r="H52" s="23" t="inlineStr"/>
       <c r="I52" s="24" t="n">
-        <v>62.856</v>
+        <v>62.8561</v>
       </c>
       <c r="J52" s="24" t="n">
-        <v>2.0171</v>
+        <v>2.0173</v>
       </c>
       <c r="K52" s="24" t="n">
         <v>15.3128</v>
       </c>
       <c r="L52" s="25" t="n">
-        <v>447.4</v>
+        <v>428.5</v>
       </c>
       <c r="M52" s="25" t="n">
         <v>25</v>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AE52" s="22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AF52" s="23" t="inlineStr">
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="D54" s="24" t="n">
-        <v>532.0599999999999</v>
+        <v>530.27</v>
       </c>
       <c r="E54" s="23" t="inlineStr"/>
       <c r="F54" s="22" t="inlineStr">
@@ -7133,7 +7133,7 @@
         <v>86.59699999999999</v>
       </c>
       <c r="L54" s="25" t="n">
-        <v>551.5</v>
+        <v>549.3</v>
       </c>
       <c r="M54" s="25" t="n">
         <v>25</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="AE54" s="22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AF54" s="23" t="inlineStr">
@@ -12230,10 +12230,10 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>346.2</v>
+        <v>343.09</v>
       </c>
       <c r="D52" s="34" t="n">
-        <v>49.1601</v>
+        <v>49.1602</v>
       </c>
       <c r="E52" s="34" t="n">
         <v>9.446</v>
@@ -12244,10 +12244,10 @@
       <c r="G52" s="34" t="inlineStr"/>
       <c r="H52" s="34" t="inlineStr"/>
       <c r="I52" s="34" t="n">
-        <v>8.898300000000001</v>
+        <v>8.8986</v>
       </c>
       <c r="J52" s="34" t="n">
-        <v>12.4163</v>
+        <v>12.4164</v>
       </c>
       <c r="K52" s="34" t="n">
         <v>494.7644</v>
@@ -12336,7 +12336,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>531.877</v>
+        <v>542.33</v>
       </c>
       <c r="D54" s="34" t="n">
         <v>1600617.8442</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="L54" s="34" t="inlineStr"/>
       <c r="M54" s="34" t="n">
-        <v>7.37</v>
+        <v>7.39</v>
       </c>
       <c r="N54" s="34" t="n">
         <v>8.800000000000001</v>
@@ -12495,10 +12495,10 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>344.1</v>
+        <v>332.17</v>
       </c>
       <c r="D57" s="34" t="n">
-        <v>62.856</v>
+        <v>62.8561</v>
       </c>
       <c r="E57" s="34" t="n">
         <v>14.6499</v>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="H57" s="34" t="inlineStr"/>
       <c r="I57" s="34" t="n">
-        <v>2.0171</v>
+        <v>2.0173</v>
       </c>
       <c r="J57" s="34" t="n">
         <v>3.797</v>
@@ -12552,10 +12552,10 @@
         </is>
       </c>
       <c r="C58" s="34" t="n">
-        <v>249.5</v>
+        <v>254.975</v>
       </c>
       <c r="D58" s="34" t="n">
-        <v>480.8226</v>
+        <v>480.8176</v>
       </c>
       <c r="E58" s="34" t="n">
         <v>9.3416</v>
@@ -12566,17 +12566,17 @@
       <c r="G58" s="34" t="inlineStr"/>
       <c r="H58" s="34" t="inlineStr"/>
       <c r="I58" s="34" t="n">
-        <v>15.5059</v>
+        <v>15.49</v>
       </c>
       <c r="J58" s="34" t="n">
-        <v>17.7724</v>
+        <v>17.7712</v>
       </c>
       <c r="K58" s="34" t="n">
         <v>6466.5299</v>
       </c>
       <c r="L58" s="34" t="inlineStr"/>
       <c r="M58" s="34" t="n">
-        <v>8.5</v>
+        <v>8.51</v>
       </c>
       <c r="N58" s="34" t="n">
         <v>8.800000000000001</v>
@@ -12591,7 +12591,7 @@
       </c>
       <c r="Q58" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 0.11, "BVPS": 35.2592}, "graham_formula": {"g(上限10%)": 0.0344, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -30.6285, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.1926, "常態NOPAT": 4616104077.0, "WACC": 0.085, "淨現金": -16922000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": -0.0032, "永續g": 0.04, "目標營業利益率": 0.1926, "WACC": 0.085, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.544}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 0.11, "BVPS": 35.2592}, "graham_formula": {"g(上限10%)": 0.0344, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -30.6285, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.1926, "常態NOPAT": 4616104077.0, "WACC": 0.0851, "淨現金": -16922000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": -0.0032, "永續g": 0.04, "目標營業利益率": 0.1926, "WACC": 0.0851, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.544}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
         </is>
       </c>
     </row>
@@ -12715,7 +12715,7 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>532.0599999999999</v>
+        <v>530.27</v>
       </c>
       <c r="D61" s="34" t="n">
         <v>81.6728</v>
@@ -15638,7 +15638,7 @@
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>346.2</v>
+        <v>343.09</v>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
@@ -15649,16 +15649,16 @@
         <v>24.5801</v>
       </c>
       <c r="F52" s="24" t="n">
-        <v>36.8701</v>
+        <v>36.8702</v>
       </c>
       <c r="G52" s="24" t="n">
-        <v>56.5341</v>
+        <v>56.5342</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>73.7402</v>
+        <v>73.7403</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>73.7402</v>
+        <v>73.7403</v>
       </c>
       <c r="J52" s="26" t="inlineStr">
         <is>
@@ -15666,10 +15666,10 @@
         </is>
       </c>
       <c r="K52" s="24" t="n">
-        <v>7.0423</v>
+        <v>6.979</v>
       </c>
       <c r="L52" s="24" t="n">
-        <v>36.8701</v>
+        <v>36.8702</v>
       </c>
     </row>
     <row r="53">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>531.877</v>
+        <v>542.33</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>344.1</v>
+        <v>332.17</v>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
@@ -15882,13 +15882,13 @@
         <v>47.142</v>
       </c>
       <c r="G57" s="24" t="n">
-        <v>72.28440000000001</v>
+        <v>72.28449999999999</v>
       </c>
       <c r="H57" s="24" t="n">
-        <v>94.28400000000001</v>
+        <v>94.2841</v>
       </c>
       <c r="I57" s="24" t="n">
-        <v>94.28400000000001</v>
+        <v>94.2841</v>
       </c>
       <c r="J57" s="26" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         </is>
       </c>
       <c r="K57" s="24" t="n">
-        <v>5.4744</v>
+        <v>5.2846</v>
       </c>
       <c r="L57" s="24" t="n">
         <v>47.142</v>
@@ -15914,7 +15914,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>249.5</v>
+        <v>254.975</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
@@ -15922,19 +15922,19 @@
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>240.4113</v>
+        <v>240.4088</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>360.6169</v>
+        <v>360.6132</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>552.946</v>
+        <v>552.9402</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>721.2338999999999</v>
+        <v>721.2263</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>721.2338999999999</v>
+        <v>721.2263</v>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
@@ -15942,10 +15942,10 @@
         </is>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.5189</v>
+        <v>0.5303</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>360.6169</v>
+        <v>360.6132</v>
       </c>
     </row>
     <row r="59">
@@ -16052,7 +16052,7 @@
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>532.0599999999999</v>
+        <v>530.27</v>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         </is>
       </c>
       <c r="K61" s="24" t="n">
-        <v>6.5145</v>
+        <v>6.4926</v>
       </c>
       <c r="L61" s="24" t="n">
         <v>61.2546</v>
@@ -21453,7 +21453,7 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>346.2</v>
+        <v>343.09</v>
       </c>
       <c r="D52" s="32" t="n">
         <v>152198000000</v>
@@ -21627,7 +21627,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>531.877</v>
+        <v>542.33</v>
       </c>
       <c r="D54" s="32" t="inlineStr"/>
       <c r="E54" s="32" t="n">
@@ -21871,7 +21871,7 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>344.1</v>
+        <v>332.17</v>
       </c>
       <c r="D57" s="32" t="n">
         <v>137196000000</v>
@@ -21959,7 +21959,7 @@
         </is>
       </c>
       <c r="C58" s="34" t="n">
-        <v>249.5</v>
+        <v>254.975</v>
       </c>
       <c r="D58" s="32" t="n">
         <v>31538000000</v>
@@ -22217,7 +22217,7 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>532.0599999999999</v>
+        <v>530.27</v>
       </c>
       <c r="D61" s="32" t="n">
         <v>90007000000</v>
@@ -26232,7 +26232,7 @@
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>346.2</v>
+        <v>343.09</v>
       </c>
       <c r="D52" s="22" t="n">
         <v>3</v>
@@ -26354,7 +26354,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>531.877</v>
+        <v>542.33</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>5</v>
@@ -26537,7 +26537,7 @@
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>344.1</v>
+        <v>332.17</v>
       </c>
       <c r="D57" s="22" t="n">
         <v>2.5</v>
@@ -26598,7 +26598,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>249.5</v>
+        <v>254.975</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>3</v>
@@ -26781,7 +26781,7 @@
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>532.0599999999999</v>
+        <v>530.27</v>
       </c>
       <c r="D61" s="22" t="n">
         <v>2.5</v>
